--- a/results/results_vfinal.xlsx
+++ b/results/results_vfinal.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipamamazonia-my.sharepoint.com/personal/celso_junior_ipam_org_br/Documents/Documentos/NatureFREL/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Celso\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="148" documentId="8_{B8B9B17F-ECAF-430F-A206-10A4D4E4E481}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FC1FD958-18CA-42D4-B03D-A6A17A6F2F16}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF887C99-5CBC-4A5A-B889-7B7C0E9E7587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19305" yWindow="0" windowWidth="19200" windowHeight="15585" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 1" sheetId="11" r:id="rId1"/>
     <sheet name="Figure 2" sheetId="15" r:id="rId2"/>
-    <sheet name="Deter Degradation 2017-2024" sheetId="16" r:id="rId3"/>
+    <sheet name="DETER Degradation 2017-2024" sheetId="17" r:id="rId3"/>
+    <sheet name="PRODES Deforestation 2017-2024" sheetId="16" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>Year</t>
   </si>
@@ -135,9 +136,6 @@
     </r>
   </si>
   <si>
-    <t>Forest Fires and Disorganized and Geometric Selective Logging</t>
-  </si>
-  <si>
     <t>Official FREL Emissions (Deforestation)</t>
   </si>
   <si>
@@ -145,6 +143,114 @@
   </si>
   <si>
     <t>Emissions from Figure 1</t>
+  </si>
+  <si>
+    <t>Forest Fires, Disordered Selective Logging and Geometric Selective Logging</t>
+  </si>
+  <si>
+    <r>
+      <t>Amazon biome (km</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cerrado biome (km</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>Deforestation Increment Area</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Accessed on</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: https://terrabrasilis.dpi.inpe.br/app/dashboard/deforestation/biomes</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Access date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:April 7, 2025</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -259,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -288,17 +394,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -659,7 +777,7 @@
                   <a:lumOff val="15000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:prstDash val="sysDash"/>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1832,9 +1950,9 @@
             </c:extLst>
           </c:dLbls>
           <c:cat>
-            <c:numRef>
+            <c:multiLvlStrRef>
               <c:f>'Figure 2'!#REF!</c:f>
-            </c:numRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1890,12 +2008,9 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="50000"/>
-                  <a:lumOff val="50000"/>
-                </a:schemeClr>
+                <a:sysClr val="windowText" lastClr="000000"/>
               </a:solidFill>
-              <a:prstDash val="sysDash"/>
+              <a:prstDash val="solid"/>
               <a:round/>
             </a:ln>
             <a:effectLst/>
@@ -1904,9 +2019,9 @@
             <c:symbol val="none"/>
           </c:marker>
           <c:cat>
-            <c:numRef>
+            <c:multiLvlStrRef>
               <c:f>'Figure 2'!#REF!</c:f>
-            </c:numRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -1978,9 +2093,9 @@
             </c:spPr>
           </c:marker>
           <c:cat>
-            <c:numRef>
+            <c:multiLvlStrRef>
               <c:f>'Figure 2'!#REF!</c:f>
-            </c:numRef>
+            </c:multiLvlStrRef>
           </c:cat>
           <c:val>
             <c:numRef>
@@ -3436,15 +3551,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>177533</xdr:colOff>
+      <xdr:colOff>640</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>148837</xdr:rowOff>
+      <xdr:rowOff>80802</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>602480</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>172065</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>2041176</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>104802</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3479,15 +3594,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>80671</xdr:colOff>
+      <xdr:colOff>80670</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>148065</xdr:rowOff>
+      <xdr:rowOff>148064</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>806098</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>171294</xdr:rowOff>
+      <xdr:colOff>1032634</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>172064</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -3797,26 +3912,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{746E9525-7C4D-42FA-A23D-D0CEA7AFCD11}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="6.33203125" customWidth="1"/>
-    <col min="2" max="2" width="4.77734375" customWidth="1"/>
-    <col min="3" max="4" width="21.77734375" customWidth="1"/>
-    <col min="5" max="5" width="4.77734375" customWidth="1"/>
-    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.140625" customWidth="1"/>
+    <col min="2" max="2" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="32.140625" customWidth="1"/>
+    <col min="7" max="7" width="31.28515625" customWidth="1"/>
+    <col min="8" max="8" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="D1" s="15" t="s">
-        <v>13</v>
       </c>
       <c r="F1" s="9" t="s">
         <v>2</v>
@@ -3828,7 +3944,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>2017</v>
       </c>
@@ -3847,7 +3963,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2018</v>
       </c>
@@ -3866,7 +3982,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>2019</v>
       </c>
@@ -3885,7 +4001,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>2020</v>
       </c>
@@ -3904,7 +4020,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>2021</v>
       </c>
@@ -3923,7 +4039,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>2022</v>
       </c>
@@ -3941,7 +4057,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>2023</v>
       </c>
@@ -3959,15 +4075,15 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -3976,7 +4092,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -3985,7 +4101,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -3994,7 +4110,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -4003,7 +4119,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -4012,7 +4128,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
@@ -4025,17 +4141,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A3ACF42-74B5-4EF7-B6B3-6008AC5E4E20}">
   <dimension ref="A1:H41"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="3" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.77734375" customWidth="1"/>
-    <col min="6" max="6" width="21.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="19.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.77734375" customWidth="1"/>
+    <col min="2" max="3" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4.7109375" customWidth="1"/>
+    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -4049,14 +4165,14 @@
         <v>4</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1" s="9" t="str">
         <f>'Figure 1'!$H$1</f>
         <v>Official National FREL</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>2017</v>
       </c>
@@ -4078,12 +4194,12 @@
         <f>'Figure 1'!$H$2</f>
         <v>673566464</v>
       </c>
-      <c r="H2" s="16">
-        <f>B2+C2</f>
+      <c r="H2" s="13">
+        <f t="shared" ref="H2:H8" si="0">B2+C2</f>
         <v>658962103.82403505</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2018</v>
       </c>
@@ -4105,12 +4221,12 @@
         <f>G2</f>
         <v>673566464</v>
       </c>
-      <c r="H3" s="16">
-        <f>B3+C3</f>
+      <c r="H3" s="13">
+        <f t="shared" si="0"/>
         <v>601112377.50218093</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>2019</v>
       </c>
@@ -4121,7 +4237,7 @@
         <v>94686661.454995841</v>
       </c>
       <c r="D4" s="6">
-        <f t="shared" ref="D4:D6" si="0">D3</f>
+        <f t="shared" ref="D4:D6" si="1">D3</f>
         <v>757596682.88132727</v>
       </c>
       <c r="F4" s="6">
@@ -4129,15 +4245,15 @@
         <v>712722888</v>
       </c>
       <c r="G4" s="6">
-        <f t="shared" ref="G4:G8" si="1">G3</f>
+        <f t="shared" ref="G4:G8" si="2">G3</f>
         <v>673566464</v>
       </c>
-      <c r="H4" s="16">
-        <f>B4+C4</f>
+      <c r="H4" s="13">
+        <f t="shared" si="0"/>
         <v>802263461.62618291</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>2020</v>
       </c>
@@ -4148,7 +4264,7 @@
         <v>149309040.01167968</v>
       </c>
       <c r="D5" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>757596682.88132727</v>
       </c>
       <c r="F5" s="6">
@@ -4156,15 +4272,15 @@
         <v>728472868</v>
       </c>
       <c r="G5" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>673566464</v>
       </c>
-      <c r="H5" s="16">
-        <f>B5+C5</f>
+      <c r="H5" s="13">
+        <f t="shared" si="0"/>
         <v>839209829.52642131</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>2021</v>
       </c>
@@ -4175,7 +4291,7 @@
         <v>66350418.975199275</v>
       </c>
       <c r="D6" s="6">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>757596682.88132727</v>
       </c>
       <c r="F6" s="6">
@@ -4183,15 +4299,15 @@
         <v>832227808</v>
       </c>
       <c r="G6" s="6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>673566464</v>
       </c>
-      <c r="H6" s="16">
-        <f>B6+C6</f>
+      <c r="H6" s="13">
+        <f t="shared" si="0"/>
         <v>886435641.92781663</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
         <v>2022</v>
       </c>
@@ -4210,15 +4326,15 @@
         <v>920735155.03783298</v>
       </c>
       <c r="G7" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>673566464</v>
       </c>
-      <c r="H7" s="16">
-        <f>B7+C7</f>
+      <c r="H7" s="13">
+        <f t="shared" si="0"/>
         <v>1025316731.0774504</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="7">
         <v>2023</v>
       </c>
@@ -4237,86 +4353,86 @@
         <v>658193102.64530003</v>
       </c>
       <c r="G8" s="8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>673566464</v>
       </c>
-      <c r="H8" s="16">
-        <f>B8+C8</f>
+      <c r="H8" s="13">
+        <f t="shared" si="0"/>
         <v>755784926.73395979</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E34" s="2"/>
     </row>
-    <row r="37" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C37" s="1"/>
       <c r="E37" s="2"/>
     </row>
-    <row r="40" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
       <c r="C40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="3:5" x14ac:dyDescent="0.3">
+    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
       <c r="E41" s="1"/>
     </row>
   </sheetData>
@@ -4326,23 +4442,23 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF00FE4-336D-4E92-B05B-E6E1C4CE89EE}">
-  <dimension ref="A1:J13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DDE237F-5805-4F40-85AC-796F9BE5D6ED}">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.109375" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
-    <col min="10" max="10" width="8.21875" customWidth="1"/>
+    <col min="1" max="1" width="8.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="31.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" s="14"/>
-    </row>
-    <row r="2" spans="1:10" ht="16.2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="15"/>
+    </row>
+    <row r="2" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -4350,7 +4466,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>2017</v>
       </c>
@@ -4358,7 +4474,7 @@
         <v>16670</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>2018</v>
       </c>
@@ -4367,7 +4483,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>2019</v>
       </c>
@@ -4375,7 +4491,7 @@
         <v>11499</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>2020</v>
       </c>
@@ -4383,7 +4499,7 @@
         <v>18724</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>2021</v>
       </c>
@@ -4391,7 +4507,7 @@
         <v>7257</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>2022</v>
       </c>
@@ -4399,7 +4515,7 @@
         <v>15795</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2023</v>
       </c>
@@ -4407,7 +4523,7 @@
         <v>12741</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>2024</v>
       </c>
@@ -4415,35 +4531,192 @@
         <v>54551</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A12" s="11" t="s">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="11"/>
-      <c r="C12" s="11"/>
-      <c r="D12" s="11"/>
-      <c r="E12" s="11"/>
-      <c r="F12" s="11"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="11"/>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A13" s="11" t="s">
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="11"/>
-      <c r="C13" s="12"/>
+      <c r="B13" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A12:I12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A12:I12"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF00FE4-336D-4E92-B05B-E6E1C4CE89EE}">
+  <dimension ref="A1:I19"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.140625" customWidth="1"/>
+    <col min="2" max="2" width="21.42578125" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5703125" customWidth="1"/>
+    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="19"/>
+      <c r="B1" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="18"/>
+    </row>
+    <row r="2" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A2" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="5">
+        <v>2017</v>
+      </c>
+      <c r="B3" s="6">
+        <v>6758.13</v>
+      </c>
+      <c r="C3" s="6">
+        <v>7117.38</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="5">
+        <v>2018</v>
+      </c>
+      <c r="B4" s="6">
+        <v>6958.47</v>
+      </c>
+      <c r="C4" s="6">
+        <v>7259.82</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="5">
+        <v>2019</v>
+      </c>
+      <c r="B5" s="6">
+        <v>10703.06</v>
+      </c>
+      <c r="C5" s="6">
+        <v>6319.02</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="5">
+        <v>2020</v>
+      </c>
+      <c r="B6" s="6">
+        <v>10355.32</v>
+      </c>
+      <c r="C6" s="6">
+        <v>7905.16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A7" s="5">
+        <v>2021</v>
+      </c>
+      <c r="B7" s="6">
+        <v>12191.12</v>
+      </c>
+      <c r="C7" s="6">
+        <v>8531.44</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="5">
+        <v>2022</v>
+      </c>
+      <c r="B8" s="6">
+        <v>12479.39</v>
+      </c>
+      <c r="C8" s="6">
+        <v>10688.73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A9" s="5">
+        <v>2023</v>
+      </c>
+      <c r="B9" s="6">
+        <v>7812.15</v>
+      </c>
+      <c r="C9" s="6">
+        <v>11011.69</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A10" s="5">
+        <v>2024</v>
+      </c>
+      <c r="B10" s="6">
+        <v>5704.24</v>
+      </c>
+      <c r="C10" s="6">
+        <v>8174.17</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F11" s="10"/>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A12" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" s="16"/>
+    </row>
+    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+    </row>
+    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A13:B13"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>

--- a/results/results_vfinal.xlsx
+++ b/results/results_vfinal.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Celso\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF887C99-5CBC-4A5A-B889-7B7C0E9E7587}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981E02EB-334B-4623-B7BF-5A74DDD2EE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19305" yWindow="0" windowWidth="19200" windowHeight="15585" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="19770" windowHeight="12855" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 1" sheetId="11" r:id="rId1"/>
     <sheet name="Figure 2" sheetId="15" r:id="rId2"/>
     <sheet name="DETER Degradation 2017-2024" sheetId="17" r:id="rId3"/>
     <sheet name="PRODES Deforestation 2017-2024" sheetId="16" r:id="rId4"/>
+    <sheet name="Brazil's REDD+ Results" sheetId="18" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
   <si>
     <t>Year</t>
   </si>
@@ -252,12 +253,63 @@
       <t>:April 7, 2025</t>
     </r>
   </si>
+  <si>
+    <t xml:space="preserve">Year </t>
+  </si>
+  <si>
+    <r>
+      <t>t CO</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="11"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Inherit"/>
+      </rPr>
+      <t xml:space="preserve"> eq/year</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Source</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>: https://redd.unfccc.int/submissions.html?country=bra</t>
+    </r>
+  </si>
+  <si>
+    <t>Average (2006-2020)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -297,8 +349,49 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <b/>
+      <vertAlign val="subscript"/>
+      <sz val="11"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Camingodos_probold"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Camingodos_probold"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -308,6 +401,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -365,7 +470,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -398,6 +503,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -413,10 +521,25 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3912,7 +4035,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{746E9525-7C4D-42FA-A23D-D0CEA7AFCD11}">
   <dimension ref="A1:H18"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
     <col min="2" max="2" width="4.140625" customWidth="1"/>
@@ -3924,7 +4047,7 @@
     <col min="8" max="8" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="48.75" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -3944,7 +4067,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="5">
         <v>2017</v>
       </c>
@@ -3963,7 +4086,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="5">
         <v>2018</v>
       </c>
@@ -3982,7 +4105,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="5">
         <v>2019</v>
       </c>
@@ -4001,7 +4124,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="5">
         <v>2020</v>
       </c>
@@ -4020,7 +4143,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="5">
         <v>2021</v>
       </c>
@@ -4039,7 +4162,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="7">
         <v>2022</v>
       </c>
@@ -4057,7 +4180,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="7">
         <v>2023</v>
       </c>
@@ -4075,15 +4198,15 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="1"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -4092,7 +4215,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" s="1"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -4101,7 +4224,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="1"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -4110,7 +4233,7 @@
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="1"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -4119,7 +4242,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8">
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -4128,7 +4251,7 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
@@ -4141,7 +4264,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A3ACF42-74B5-4EF7-B6B3-6008AC5E4E20}">
   <dimension ref="A1:H41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="2" max="3" width="36.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="27.85546875" bestFit="1" customWidth="1"/>
@@ -4151,7 +4274,7 @@
     <col min="9" max="9" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -4172,7 +4295,7 @@
         <v>Official National FREL</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8">
       <c r="A2" s="5">
         <v>2017</v>
       </c>
@@ -4199,7 +4322,7 @@
         <v>658962103.82403505</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8">
       <c r="A3" s="5">
         <v>2018</v>
       </c>
@@ -4226,7 +4349,7 @@
         <v>601112377.50218093</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8">
       <c r="A4" s="5">
         <v>2019</v>
       </c>
@@ -4253,7 +4376,7 @@
         <v>802263461.62618291</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8">
       <c r="A5" s="5">
         <v>2020</v>
       </c>
@@ -4280,7 +4403,7 @@
         <v>839209829.52642131</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8">
       <c r="A6" s="5">
         <v>2021</v>
       </c>
@@ -4307,7 +4430,7 @@
         <v>886435641.92781663</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8">
       <c r="A7" s="7">
         <v>2022</v>
       </c>
@@ -4334,7 +4457,7 @@
         <v>1025316731.0774504</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8">
       <c r="A8" s="7">
         <v>2023</v>
       </c>
@@ -4361,78 +4484,78 @@
         <v>755784926.73395979</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8">
       <c r="A12" s="3"/>
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8">
       <c r="A13" s="3"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8">
       <c r="A16" s="3"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5">
       <c r="A18" s="3"/>
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5">
       <c r="E31" s="1"/>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5">
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:5">
       <c r="C33" s="1"/>
       <c r="E33" s="1"/>
     </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:5">
       <c r="E34" s="2"/>
     </row>
-    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:5">
       <c r="C37" s="1"/>
       <c r="E37" s="2"/>
     </row>
-    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="3:5">
       <c r="C40" s="1"/>
       <c r="E40" s="1"/>
     </row>
-    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="3:5">
       <c r="E41" s="1"/>
     </row>
   </sheetData>
@@ -4444,7 +4567,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DDE237F-5805-4F40-85AC-796F9BE5D6ED}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.140625" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
@@ -4452,13 +4575,13 @@
     <col min="10" max="10" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:9" ht="49.5" customHeight="1">
+      <c r="A1" s="15" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="15"/>
-    </row>
-    <row r="2" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="B1" s="16"/>
+    </row>
+    <row r="2" spans="1:9" ht="17.25">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -4466,7 +4589,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="5">
         <v>2017</v>
       </c>
@@ -4474,7 +4597,7 @@
         <v>16670</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="5">
         <v>2018</v>
       </c>
@@ -4483,7 +4606,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="5">
         <v>2019</v>
       </c>
@@ -4491,7 +4614,7 @@
         <v>11499</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="5">
         <v>2020</v>
       </c>
@@ -4499,7 +4622,7 @@
         <v>18724</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="5">
         <v>2021</v>
       </c>
@@ -4507,7 +4630,7 @@
         <v>7257</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" s="5">
         <v>2022</v>
       </c>
@@ -4515,7 +4638,7 @@
         <v>15795</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="5">
         <v>2023</v>
       </c>
@@ -4523,7 +4646,7 @@
         <v>12741</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="5">
         <v>2024</v>
       </c>
@@ -4531,27 +4654,27 @@
         <v>54551</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+    <row r="12" spans="1:9">
+      <c r="A12" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="16"/>
+      <c r="B13" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4566,7 +4689,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF00FE4-336D-4E92-B05B-E6E1C4CE89EE}">
   <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.140625" customWidth="1"/>
     <col min="2" max="2" width="21.42578125" customWidth="1"/>
@@ -4575,14 +4698,14 @@
     <col min="10" max="10" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="19"/>
-      <c r="B1" s="17" t="s">
+    <row r="1" spans="1:9">
+      <c r="A1" s="14"/>
+      <c r="B1" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="18"/>
-    </row>
-    <row r="2" spans="1:9" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="C1" s="19"/>
+    </row>
+    <row r="2" spans="1:9" ht="17.25">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -4593,7 +4716,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9">
       <c r="A3" s="5">
         <v>2017</v>
       </c>
@@ -4604,7 +4727,7 @@
         <v>7117.38</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9">
       <c r="A4" s="5">
         <v>2018</v>
       </c>
@@ -4616,7 +4739,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9">
       <c r="A5" s="5">
         <v>2019</v>
       </c>
@@ -4627,7 +4750,7 @@
         <v>6319.02</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9">
       <c r="A6" s="5">
         <v>2020</v>
       </c>
@@ -4638,7 +4761,7 @@
         <v>7905.16</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9">
       <c r="A7" s="5">
         <v>2021</v>
       </c>
@@ -4649,7 +4772,7 @@
         <v>8531.44</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9">
       <c r="A8" s="5">
         <v>2022</v>
       </c>
@@ -4660,7 +4783,7 @@
         <v>10688.73</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9">
       <c r="A9" s="5">
         <v>2023</v>
       </c>
@@ -4671,7 +4794,7 @@
         <v>11011.69</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9">
       <c r="A10" s="5">
         <v>2024</v>
       </c>
@@ -4682,33 +4805,31 @@
         <v>8174.17</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9">
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A12" s="16" t="s">
+    <row r="12" spans="1:9">
+      <c r="A12" s="17" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="20"/>
-      <c r="H12" s="20"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
       <c r="I12" s="11"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A13" s="16" t="s">
+    <row r="13" spans="1:9">
+      <c r="A13" s="17" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="16"/>
-    </row>
-    <row r="18" spans="3:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="17"/>
+    </row>
+    <row r="18" spans="3:4">
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
     </row>
-    <row r="19" spans="3:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="3:4">
       <c r="C19" s="2"/>
       <c r="D19" s="2"/>
     </row>
@@ -4720,4 +4841,240 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8347AE-1F9E-406B-BBBE-0167BC334EA0}">
+  <dimension ref="A1:J26"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.28515625" customWidth="1"/>
+    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" ht="16.5">
+      <c r="A1" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D1" s="21" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="22">
+        <v>2006</v>
+      </c>
+      <c r="B2" s="23">
+        <v>529930490.25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="22">
+        <v>2007</v>
+      </c>
+      <c r="B3" s="24">
+        <v>497761219.37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="22">
+        <v>2008</v>
+      </c>
+      <c r="B4" s="24">
+        <v>440022301.24000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="22">
+        <v>2009</v>
+      </c>
+      <c r="B5" s="23">
+        <v>741687139.44000006</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="22">
+        <v>2010</v>
+      </c>
+      <c r="B6" s="23">
+        <v>761621104.20000005</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="22">
+        <v>2011</v>
+      </c>
+      <c r="B7" s="23">
+        <v>622451671.72000003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="22">
+        <v>2012</v>
+      </c>
+      <c r="B8" s="23">
+        <v>671275311.88999999</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="22">
+        <v>2013</v>
+      </c>
+      <c r="B9" s="23">
+        <v>606111615.41999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="22">
+        <v>2014</v>
+      </c>
+      <c r="B10" s="23">
+        <v>634367865.74000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="22">
+        <v>2015</v>
+      </c>
+      <c r="B11" s="23">
+        <v>620295262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="22">
+        <v>2011</v>
+      </c>
+      <c r="B12" s="23">
+        <v>159099238</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="22">
+        <v>2012</v>
+      </c>
+      <c r="B13" s="24">
+        <v>159099238</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="22">
+        <v>2013</v>
+      </c>
+      <c r="B14" s="24">
+        <v>136203956</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="22">
+        <v>2014</v>
+      </c>
+      <c r="B15" s="24">
+        <v>170181166</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="22">
+        <v>2015</v>
+      </c>
+      <c r="B16" s="24">
+        <v>157885429</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="22">
+        <v>2016</v>
+      </c>
+      <c r="B17" s="24">
+        <v>234428859</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="22">
+        <v>2017</v>
+      </c>
+      <c r="B18" s="24">
+        <v>221098119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="22">
+        <v>2016</v>
+      </c>
+      <c r="B19" s="23">
+        <v>377344006.02999997</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="22">
+        <v>2017</v>
+      </c>
+      <c r="B20" s="24">
+        <v>391656866.92000002</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="22">
+        <v>2018</v>
+      </c>
+      <c r="B21" s="23">
+        <v>345428734.49000001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="22">
+        <v>2019</v>
+      </c>
+      <c r="B22" s="24">
+        <v>173538420.53999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="22">
+        <v>2018</v>
+      </c>
+      <c r="B23" s="23">
+        <v>232957994</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="22">
+        <v>2019</v>
+      </c>
+      <c r="B24" s="24">
+        <v>237138558</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="22">
+        <v>2020</v>
+      </c>
+      <c r="B25" s="24">
+        <v>227389933</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="B26" s="26">
+        <f>AVERAGE(B2:B25)</f>
+        <v>389540604.13541669</v>
+      </c>
+      <c r="E26" s="10"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="D1:J1"/>
+  </mergeCells>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/results/results_vfinal.xlsx
+++ b/results/results_vfinal.xlsx
@@ -1,25 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Celso\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Celso\Documents\GitHub\Brazil-National-FREL\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{981E02EB-334B-4623-B7BF-5A74DDD2EE57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2C95EF-3402-44DC-AD55-6CFF0EAF20AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1905" yWindow="1905" windowWidth="19770" windowHeight="12855" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="29775" windowHeight="15585" tabRatio="761" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 1" sheetId="11" r:id="rId1"/>
-    <sheet name="Figure 2" sheetId="15" r:id="rId2"/>
+    <sheet name="Figure 4" sheetId="15" r:id="rId2"/>
     <sheet name="DETER Degradation 2017-2024" sheetId="17" r:id="rId3"/>
     <sheet name="PRODES Deforestation 2017-2024" sheetId="16" r:id="rId4"/>
     <sheet name="Brazil's REDD+ Results" sheetId="18" r:id="rId5"/>
+    <sheet name="2022 and 2023 Emissions" sheetId="19" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="42">
   <si>
     <t>Year</t>
   </si>
@@ -304,12 +306,68 @@
   <si>
     <t>Average (2006-2020)</t>
   </si>
+  <si>
+    <t>5,704.24*</t>
+  </si>
+  <si>
+    <t>*Based on priority tile mapping. Source: https://data.inpe.br/big/web/biomasbr/notas-tecnicas/estimativa-de-desmatamento-na-amazonia-legal-para/</t>
+  </si>
+  <si>
+    <t>Amazonia</t>
+  </si>
+  <si>
+    <t>Cerrado</t>
+  </si>
+  <si>
+    <t>Caatinga</t>
+  </si>
+  <si>
+    <t>Atlantic Forest</t>
+  </si>
+  <si>
+    <t>Pampa</t>
+  </si>
+  <si>
+    <t>Pantanal</t>
+  </si>
+  <si>
+    <t>Brazil</t>
+  </si>
+  <si>
+    <t>Biome</t>
+  </si>
+  <si>
+    <t>Official FREL (t CO₂ eq)</t>
+  </si>
+  <si>
+    <t>Gross Deforestation (t CO₂ eq)</t>
+  </si>
+  <si>
+    <t>Net Deforestation (t CO₂ eq)</t>
+  </si>
+  <si>
+    <t>Gross Degradation (t CO₂ eq)</t>
+  </si>
+  <si>
+    <t>Deforestation + Degradation (t CO₂ eq)</t>
+  </si>
+  <si>
+    <t>Corrected Total Emissions (t CO₂ eq)</t>
+  </si>
+  <si>
+    <t>Estimated Result for 2022
+(t CO₂ eq)</t>
+  </si>
+  <si>
+    <t>Estimated Result for 2023
+(%)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12">
+  <fonts count="15">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -389,6 +447,26 @@
       <sz val="11"/>
       <color theme="0"/>
       <name val="Camingodos_probold"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -470,7 +548,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -496,9 +574,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -506,6 +581,64 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="4" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="12" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="4" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -521,25 +654,10 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="1" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="4" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="4" fontId="11" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -706,10 +824,10 @@
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="5">
-                  <c:v>920735155.03783298</c:v>
+                  <c:v>920000848.54453743</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>658193102.64530003</c:v>
+                  <c:v>656934443.71267962</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1486,7 +1604,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Figure 2'!$B$1</c:f>
+              <c:f>'Figure 4'!$B$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1564,7 +1682,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Figure 2'!$A$2:$A$8</c:f>
+              <c:f>'Figure 4'!$A$2:$A$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1594,30 +1712,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Figure 2'!$B$2:$B$8</c:f>
+              <c:f>'Figure 4'!$B$2:$B$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>533165823.25416672</c:v>
+                  <c:v>504814968.13472211</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>541331921.62073648</c:v>
+                  <c:v>512747778.48476946</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>707576800.17118704</c:v>
+                  <c:v>669640433.63217413</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>689900789.51474166</c:v>
+                  <c:v>651615154.05905795</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>820085222.95261741</c:v>
+                  <c:v>774439089.33926058</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>899553082.27684653</c:v>
+                  <c:v>848533360.49760962</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>629969720.22822881</c:v>
+                  <c:v>592190242.8729775</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1633,7 +1751,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Figure 2'!$C$1</c:f>
+              <c:f>'Figure 4'!$C$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1655,6 +1773,27 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:dLbls>
+            <c:dLbl>
+              <c:idx val="0"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="-2.0751633986928104E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-3C48-4674-B444-3E9FCB64E3CE}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
             <c:dLbl>
               <c:idx val="1"/>
               <c:layout>
@@ -1681,7 +1820,7 @@
               <c:layout>
                 <c:manualLayout>
                   <c:x val="0"/>
-                  <c:y val="-5.9514375881435343E-2"/>
+                  <c:y val="-6.573986928104579E-2"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -1740,11 +1879,32 @@
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
+              <c:idx val="5"/>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0"/>
+                  <c:y val="-7.8856209150326775E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:showLegendKey val="0"/>
+              <c:showVal val="1"/>
+              <c:showCatName val="0"/>
+              <c:showSerName val="0"/>
+              <c:showPercent val="0"/>
+              <c:showBubbleSize val="0"/>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-3C48-4674-B444-3E9FCB64E3CE}"/>
+                </c:ext>
+              </c:extLst>
+            </c:dLbl>
+            <c:dLbl>
               <c:idx val="6"/>
               <c:layout>
                 <c:manualLayout>
                   <c:x val="0"/>
-                  <c:y val="-8.5771090414989773E-2"/>
+                  <c:y val="-0.10029722222222222"/>
                 </c:manualLayout>
               </c:layout>
               <c:showLegendKey val="0"/>
@@ -1804,7 +1964,7 @@
           </c:dLbls>
           <c:cat>
             <c:numRef>
-              <c:f>'Figure 2'!$A$2:$A$8</c:f>
+              <c:f>'Figure 4'!$A$2:$A$8</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="7"/>
@@ -1834,30 +1994,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Figure 2'!$C$2:$C$8</c:f>
+              <c:f>'Figure 4'!$C$2:$C$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>125796280.56986836</c:v>
+                  <c:v>138177772.22768989</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>59780455.881444469</c:v>
+                  <c:v>64328318.518658698</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>94686661.454995841</c:v>
+                  <c:v>101663449.22992247</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>149309040.01167968</c:v>
+                  <c:v>161190520.30257586</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>66350418.975199275</c:v>
+                  <c:v>68652293.948963672</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>125763648.80060382</c:v>
+                  <c:v>134676822.19909376</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>125815206.50573097</c:v>
+                  <c:v>133936755.6163467</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1889,7 +2049,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Figure 2'!$D$1</c:f>
+              <c:f>'Figure 4'!$D$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2079,30 +2239,30 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Figure 2'!$D$2:$D$8</c:f>
+              <c:f>'Figure 4'!$D$2:$D$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
                 <c:pt idx="0">
-                  <c:v>757596682.88132727</c:v>
+                  <c:v>729453955.5755589</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>757596682.88132727</c:v>
+                  <c:v>729453955.5755589</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>757596682.88132727</c:v>
+                  <c:v>729453955.5755589</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>757596682.88132727</c:v>
+                  <c:v>729453955.5755589</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>757596682.88132727</c:v>
+                  <c:v>729453955.5755589</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>757596682.88132727</c:v>
+                  <c:v>729453955.5755589</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>757596682.88132727</c:v>
+                  <c:v>729453955.5755589</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2119,7 +2279,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>'Figure 2'!$G$1</c:f>
+              <c:f>'Figure 4'!$G$1</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2148,7 +2308,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Figure 2'!$G$2:$G$8</c:f>
+              <c:f>'Figure 4'!$G$2:$G$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2222,7 +2382,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'Figure 2'!$F$2:$F$8</c:f>
+              <c:f>'Figure 4'!$F$2:$F$8</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="7"/>
@@ -2242,10 +2402,10 @@
                   <c:v>832227808</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>920735155.03783298</c:v>
+                  <c:v>920000848.54453743</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>658193102.64530003</c:v>
+                  <c:v>656934443.71267962</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2437,6 +2597,7 @@
         <c:crossAx val="566953023"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:minorUnit val="20000000"/>
         <c:dispUnits>
           <c:builtInUnit val="millions"/>
           <c:dispUnitsLbl>
@@ -3717,15 +3878,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>80670</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>148064</xdr:rowOff>
+      <xdr:colOff>420849</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>80028</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>1032634</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>172064</xdr:rowOff>
+      <xdr:colOff>1100670</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>104028</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -4034,7 +4195,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{746E9525-7C4D-42FA-A23D-D0CEA7AFCD11}">
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:L26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.140625" customWidth="1"/>
@@ -4045,16 +4206,18 @@
     <col min="6" max="6" width="32.140625" customWidth="1"/>
     <col min="7" max="7" width="31.28515625" customWidth="1"/>
     <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="19.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="48.75" customHeight="1">
+    <row r="1" spans="1:12" ht="48.75" customHeight="1">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="11" t="s">
         <v>12</v>
       </c>
       <c r="F1" s="9" t="s">
@@ -4067,7 +4230,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:12">
       <c r="A2" s="5">
         <v>2017</v>
       </c>
@@ -4086,7 +4249,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:12">
       <c r="A3" s="5">
         <v>2018</v>
       </c>
@@ -4105,7 +4268,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:12">
       <c r="A4" s="5">
         <v>2019</v>
       </c>
@@ -4124,7 +4287,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:12">
       <c r="A5" s="5">
         <v>2020</v>
       </c>
@@ -4143,7 +4306,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:12">
       <c r="A6" s="5">
         <v>2021</v>
       </c>
@@ -4162,7 +4325,7 @@
         <v>673566464</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:12">
       <c r="A7" s="7">
         <v>2022</v>
       </c>
@@ -4174,13 +4337,20 @@
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8">
-        <v>920735155.03783298</v>
+        <f>'2022 and 2023 Emissions'!H14</f>
+        <v>920000848.54453743</v>
       </c>
       <c r="H7" s="8">
         <v>673566464</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="J7" s="1"/>
+      <c r="K7" s="1">
+        <f>H7-G7</f>
+        <v>-246434384.54453743</v>
+      </c>
+      <c r="L7" s="10"/>
+    </row>
+    <row r="8" spans="1:12">
       <c r="A8" s="7">
         <v>2023</v>
       </c>
@@ -4192,21 +4362,28 @@
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8">
-        <v>658193102.64530003</v>
+        <f>'2022 and 2023 Emissions'!H15</f>
+        <v>656934443.71267962</v>
       </c>
       <c r="H8" s="8">
         <v>673566464</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="J8" s="1"/>
+      <c r="K8" s="1">
+        <f>H8-G8</f>
+        <v>16632020.287320375</v>
+      </c>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="11" spans="1:12">
       <c r="B11" s="3"/>
       <c r="C11" s="3"/>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:12">
       <c r="B12" s="4"/>
       <c r="C12" s="4"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:12">
       <c r="A13" s="1"/>
       <c r="B13" s="4"/>
       <c r="C13" s="4"/>
@@ -4215,7 +4392,7 @@
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:12">
       <c r="A14" s="1"/>
       <c r="B14" s="4"/>
       <c r="C14" s="4"/>
@@ -4223,8 +4400,9 @@
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="1"/>
       <c r="B15" s="4"/>
       <c r="C15" s="4"/>
@@ -4232,8 +4410,9 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="J15" s="2"/>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="1"/>
       <c r="B16" s="4"/>
       <c r="C16" s="4"/>
@@ -4242,7 +4421,7 @@
       <c r="G16" s="1"/>
       <c r="H16" s="1"/>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:10">
       <c r="A17" s="1"/>
       <c r="B17" s="4"/>
       <c r="C17" s="4"/>
@@ -4251,9 +4430,16 @@
       <c r="G17" s="1"/>
       <c r="H17" s="1"/>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:10">
       <c r="B18" s="4"/>
       <c r="C18" s="4"/>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="J23" s="1"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="J26" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -4263,18 +4449,22 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A3ACF42-74B5-4EF7-B6B3-6008AC5E4E20}">
-  <dimension ref="A1:H41"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="3" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="21.85546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="19.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.42578125" customWidth="1"/>
+    <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" customWidth="1"/>
+    <col min="6" max="6" width="32.28515625" customWidth="1"/>
+    <col min="7" max="7" width="30.42578125" customWidth="1"/>
+    <col min="8" max="8" width="10.7109375" customWidth="1"/>
+    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" customWidth="1"/>
+    <col min="13" max="13" width="13.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:15">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -4295,19 +4485,19 @@
         <v>Official National FREL</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:15">
       <c r="A2" s="5">
         <v>2017</v>
       </c>
       <c r="B2" s="6">
-        <v>533165823.25416672</v>
+        <v>504814968.13472211</v>
       </c>
       <c r="C2" s="6">
-        <v>125796280.56986836</v>
+        <v>138177772.22768989</v>
       </c>
       <c r="D2" s="6">
         <f>AVERAGE(H2:H6)</f>
-        <v>757596682.88132727</v>
+        <v>729453955.5755589</v>
       </c>
       <c r="F2" s="6">
         <f>'Figure 1'!F2</f>
@@ -4317,24 +4507,24 @@
         <f>'Figure 1'!$H$2</f>
         <v>673566464</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="12">
         <f t="shared" ref="H2:H8" si="0">B2+C2</f>
-        <v>658962103.82403505</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8">
+        <v>642992740.36241198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
       <c r="A3" s="5">
         <v>2018</v>
       </c>
       <c r="B3" s="6">
-        <v>541331921.62073648</v>
+        <v>512747778.48476946</v>
       </c>
       <c r="C3" s="6">
-        <v>59780455.881444469</v>
+        <v>64328318.518658698</v>
       </c>
       <c r="D3" s="6">
         <f>D2</f>
-        <v>757596682.88132727</v>
+        <v>729453955.5755589</v>
       </c>
       <c r="F3" s="6">
         <f>'Figure 1'!F3</f>
@@ -4344,24 +4534,24 @@
         <f>G2</f>
         <v>673566464</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="12">
         <f t="shared" si="0"/>
-        <v>601112377.50218093</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>577076097.00342822</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" s="5">
         <v>2019</v>
       </c>
       <c r="B4" s="6">
-        <v>707576800.17118704</v>
+        <v>669640433.63217413</v>
       </c>
       <c r="C4" s="6">
-        <v>94686661.454995841</v>
+        <v>101663449.22992247</v>
       </c>
       <c r="D4" s="6">
         <f t="shared" ref="D4:D6" si="1">D3</f>
-        <v>757596682.88132727</v>
+        <v>729453955.5755589</v>
       </c>
       <c r="F4" s="6">
         <f>'Figure 1'!F4</f>
@@ -4371,24 +4561,24 @@
         <f t="shared" ref="G4:G8" si="2">G3</f>
         <v>673566464</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="12">
         <f t="shared" si="0"/>
-        <v>802263461.62618291</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8">
+        <v>771303882.86209655</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" s="5">
         <v>2020</v>
       </c>
       <c r="B5" s="6">
-        <v>689900789.51474166</v>
+        <v>651615154.05905795</v>
       </c>
       <c r="C5" s="6">
-        <v>149309040.01167968</v>
+        <v>161190520.30257586</v>
       </c>
       <c r="D5" s="6">
         <f t="shared" si="1"/>
-        <v>757596682.88132727</v>
+        <v>729453955.5755589</v>
       </c>
       <c r="F5" s="6">
         <f>'Figure 1'!F5</f>
@@ -4398,24 +4588,24 @@
         <f t="shared" si="2"/>
         <v>673566464</v>
       </c>
-      <c r="H5" s="13">
+      <c r="H5" s="12">
         <f t="shared" si="0"/>
-        <v>839209829.52642131</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>812805674.36163378</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="A6" s="5">
         <v>2021</v>
       </c>
       <c r="B6" s="6">
-        <v>820085222.95261741</v>
+        <v>774439089.33926058</v>
       </c>
       <c r="C6" s="6">
-        <v>66350418.975199275</v>
+        <v>68652293.948963672</v>
       </c>
       <c r="D6" s="6">
         <f t="shared" si="1"/>
-        <v>757596682.88132727</v>
+        <v>729453955.5755589</v>
       </c>
       <c r="F6" s="6">
         <f>'Figure 1'!F6</f>
@@ -4425,138 +4615,232 @@
         <f t="shared" si="2"/>
         <v>673566464</v>
       </c>
-      <c r="H6" s="13">
+      <c r="H6" s="12">
         <f t="shared" si="0"/>
-        <v>886435641.92781663</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>843091383.28822422</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="A7" s="7">
         <v>2022</v>
       </c>
       <c r="B7" s="8">
-        <v>899553082.27684653</v>
+        <v>848533360.49760962</v>
       </c>
       <c r="C7" s="8">
-        <v>125763648.80060382</v>
+        <v>134676822.19909376</v>
       </c>
       <c r="D7" s="8">
         <f>D6</f>
-        <v>757596682.88132727</v>
+        <v>729453955.5755589</v>
       </c>
       <c r="F7" s="8">
         <f>'Figure 1'!G7</f>
-        <v>920735155.03783298</v>
+        <v>920000848.54453743</v>
       </c>
       <c r="G7" s="8">
         <f t="shared" si="2"/>
         <v>673566464</v>
       </c>
-      <c r="H7" s="13">
-        <f t="shared" si="0"/>
-        <v>1025316731.0774504</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="H7" s="12">
+        <f>B7+C7</f>
+        <v>983210182.69670343</v>
+      </c>
+      <c r="I7" s="1">
+        <f>D7-H7</f>
+        <v>-253756227.12114453</v>
+      </c>
+      <c r="K7" s="1">
+        <f>'Figure 1'!K7</f>
+        <v>-246434384.54453743</v>
+      </c>
+      <c r="M7" s="1">
+        <f>(I7*-1)-(K7*-1)</f>
+        <v>7321842.5766071081</v>
+      </c>
+      <c r="O7" s="2">
+        <f>M7/(K7*-1)*100</f>
+        <v>2.9711124079293616</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" s="7">
         <v>2023</v>
       </c>
       <c r="B8" s="8">
-        <v>629969720.22822881</v>
+        <v>592190242.8729775</v>
       </c>
       <c r="C8" s="8">
-        <v>125815206.50573097</v>
+        <v>133936755.6163467</v>
       </c>
       <c r="D8" s="8">
         <f>D7</f>
-        <v>757596682.88132727</v>
+        <v>729453955.5755589</v>
       </c>
       <c r="F8" s="8">
         <f>'Figure 1'!G8</f>
-        <v>658193102.64530003</v>
+        <v>656934443.71267962</v>
       </c>
       <c r="G8" s="8">
         <f t="shared" si="2"/>
         <v>673566464</v>
       </c>
-      <c r="H8" s="13">
+      <c r="H8" s="12">
         <f t="shared" si="0"/>
-        <v>755784926.73395979</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>726126998.48932421</v>
+      </c>
+      <c r="I8" s="1">
+        <f>D8-H8</f>
+        <v>3326957.0862346888</v>
+      </c>
+      <c r="K8" s="1">
+        <f>'Figure 1'!K8</f>
+        <v>16632020.287320375</v>
+      </c>
+      <c r="M8" s="1">
+        <f>(K8)-(I8)</f>
+        <v>13305063.201085687</v>
+      </c>
+      <c r="O8" s="2">
+        <f>M8/(K8)*100</f>
+        <v>79.996674915247453</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-    </row>
-    <row r="12" spans="1:8">
+    </row>
+    <row r="12" spans="1:15">
       <c r="A12" s="3"/>
       <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-    </row>
-    <row r="13" spans="1:8">
+    </row>
+    <row r="13" spans="1:15">
       <c r="A13" s="3"/>
       <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
+      <c r="C13" s="1"/>
       <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-    </row>
-    <row r="14" spans="1:8">
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" s="3"/>
       <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="L14" s="2">
+        <f>'Figure 1'!D2/'Figure 4'!C2*100</f>
+        <v>35.654804825495098</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
+      <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="L15" s="2">
+        <f>'Figure 1'!D3/'Figure 4'!C3*100</f>
+        <v>27.023722056340905</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="A16" s="3"/>
       <c r="B16" s="4"/>
-      <c r="C16" s="4"/>
+      <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-    </row>
-    <row r="17" spans="1:5">
+      <c r="L16" s="2">
+        <f>'Figure 1'!D4/'Figure 4'!C4*100</f>
+        <v>33.463662956250403</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
-      <c r="C17" s="4"/>
+      <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-    </row>
-    <row r="18" spans="1:5">
+      <c r="L17" s="2">
+        <f>'Figure 1'!D5/'Figure 4'!C5*100</f>
+        <v>41.23688655835786</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="3"/>
       <c r="B18" s="4"/>
-      <c r="C18" s="4"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="E31" s="1"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="C32" s="1"/>
-    </row>
-    <row r="33" spans="3:5">
-      <c r="C33" s="1"/>
-      <c r="E33" s="1"/>
-    </row>
-    <row r="34" spans="3:5">
-      <c r="E34" s="2"/>
-    </row>
-    <row r="37" spans="3:5">
-      <c r="C37" s="1"/>
-      <c r="E37" s="2"/>
-    </row>
-    <row r="40" spans="3:5">
-      <c r="C40" s="1"/>
-      <c r="E40" s="1"/>
-    </row>
-    <row r="41" spans="3:5">
-      <c r="E41" s="1"/>
+      <c r="L18" s="2">
+        <f>'Figure 1'!D6/'Figure 4'!C6*100</f>
+        <v>55.930257812717443</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="L20" s="2">
+        <f>AVERAGE(L14:L18)</f>
+        <v>38.661866841832342</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="G22">
+        <v>673566464</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="G24" s="1">
+        <f>D8-G22</f>
+        <v>55887491.575558901</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="G25" s="33">
+        <f>G24/G22*100</f>
+        <v>8.2972497240537937</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="G29" s="2">
+        <f>C2/'Figure 1'!D2</f>
+        <v>2.8046710812029083</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="G30" s="2">
+        <f>C3/'Figure 1'!D3</f>
+        <v>3.7004525058211137</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="D31" s="1"/>
+      <c r="G31" s="2">
+        <f>C4/'Figure 1'!D4</f>
+        <v>2.98831601701038</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="G32" s="2">
+        <f>C5/'Figure 1'!D5</f>
+        <v>2.4250133399009504</v>
+      </c>
+    </row>
+    <row r="33" spans="4:7">
+      <c r="D33" s="1"/>
+      <c r="G33" s="2">
+        <f>C6/'Figure 1'!D6</f>
+        <v>1.7879409806200099</v>
+      </c>
+    </row>
+    <row r="34" spans="4:7">
+      <c r="D34" s="2"/>
+      <c r="G34" s="2">
+        <f>AVERAGE(G29:G33)</f>
+        <v>2.741278784911072</v>
+      </c>
+    </row>
+    <row r="35" spans="4:7">
+      <c r="G35" s="2"/>
+    </row>
+    <row r="37" spans="4:7">
+      <c r="D37" s="2"/>
+    </row>
+    <row r="40" spans="4:7">
+      <c r="D40" s="1"/>
+    </row>
+    <row r="41" spans="4:7">
+      <c r="D41" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -4576,10 +4860,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="49.5" customHeight="1">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="16"/>
+      <c r="B1" s="35"/>
     </row>
     <row r="2" spans="1:9" ht="17.25">
       <c r="A2" s="9" t="s">
@@ -4658,23 +4942,23 @@
       <c r="F11" s="10"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="36"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="B13" s="17"/>
+      <c r="B13" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -4688,7 +4972,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF00FE4-336D-4E92-B05B-E6E1C4CE89EE}">
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8.140625" customWidth="1"/>
@@ -4698,14 +4982,14 @@
     <col min="10" max="10" width="8.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="14"/>
-      <c r="B1" s="18" t="s">
+    <row r="1" spans="1:13">
+      <c r="A1" s="13"/>
+      <c r="B1" s="37" t="s">
         <v>17</v>
       </c>
-      <c r="C1" s="19"/>
-    </row>
-    <row r="2" spans="1:9" ht="17.25">
+      <c r="C1" s="38"/>
+    </row>
+    <row r="2" spans="1:13" ht="17.25">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -4716,7 +5000,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:13">
       <c r="A3" s="5">
         <v>2017</v>
       </c>
@@ -4727,7 +5011,7 @@
         <v>7117.38</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:13">
       <c r="A4" s="5">
         <v>2018</v>
       </c>
@@ -4739,7 +5023,7 @@
       </c>
       <c r="D4" s="1"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:13">
       <c r="A5" s="5">
         <v>2019</v>
       </c>
@@ -4750,7 +5034,7 @@
         <v>6319.02</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:13">
       <c r="A6" s="5">
         <v>2020</v>
       </c>
@@ -4761,7 +5045,7 @@
         <v>7905.16</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:13">
       <c r="A7" s="5">
         <v>2021</v>
       </c>
@@ -4772,7 +5056,7 @@
         <v>8531.44</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:13">
       <c r="A8" s="5">
         <v>2022</v>
       </c>
@@ -4783,7 +5067,7 @@
         <v>10688.73</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:13">
       <c r="A9" s="5">
         <v>2023</v>
       </c>
@@ -4794,36 +5078,70 @@
         <v>11011.69</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:13">
       <c r="A10" s="5">
         <v>2024</v>
       </c>
-      <c r="B10" s="6">
-        <v>5704.24</v>
+      <c r="B10" s="6" t="s">
+        <v>24</v>
       </c>
       <c r="C10" s="6">
         <v>8174.17</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:13">
       <c r="F11" s="10"/>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="17" t="s">
+    <row r="12" spans="1:13">
+      <c r="A12" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="I12" s="11"/>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="17" t="s">
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="39"/>
+      <c r="K12" s="39"/>
+      <c r="L12" s="39"/>
+      <c r="M12" s="20"/>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="B13" s="17"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39"/>
+      <c r="F13" s="39"/>
+      <c r="G13" s="39"/>
+      <c r="H13" s="39"/>
+      <c r="I13" s="39"/>
+      <c r="J13" s="39"/>
+      <c r="K13" s="39"/>
+      <c r="L13" s="39"/>
+      <c r="M13" s="20"/>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="39" t="s">
+        <v>25</v>
+      </c>
+      <c r="B14" s="39"/>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="39"/>
+      <c r="G14" s="39"/>
+      <c r="H14" s="39"/>
+      <c r="I14" s="39"/>
+      <c r="J14" s="39"/>
+      <c r="K14" s="39"/>
+      <c r="L14" s="39"/>
+      <c r="M14" s="21"/>
     </row>
     <row r="18" spans="3:4">
       <c r="C18" s="1"/>
@@ -4834,10 +5152,11 @@
       <c r="D19" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="A12:F12"/>
-    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A14:L14"/>
+    <mergeCell ref="A13:L13"/>
+    <mergeCell ref="A12:L12"/>
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
@@ -4845,231 +5164,236 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8347AE-1F9E-406B-BBBE-0167BC334EA0}">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.28515625" customWidth="1"/>
     <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.5">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="40" t="s">
         <v>22</v>
       </c>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="22">
+      <c r="A2" s="15">
         <v>2006</v>
       </c>
-      <c r="B2" s="23">
+      <c r="B2" s="16">
         <v>529930490.25</v>
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="22">
+      <c r="A3" s="15">
         <v>2007</v>
       </c>
-      <c r="B3" s="24">
+      <c r="B3" s="17">
         <v>497761219.37</v>
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="22">
+      <c r="A4" s="15">
         <v>2008</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="17">
         <v>440022301.24000001</v>
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="22">
+      <c r="A5" s="15">
         <v>2009</v>
       </c>
-      <c r="B5" s="23">
+      <c r="B5" s="16">
         <v>741687139.44000006</v>
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="22">
+      <c r="A6" s="15">
         <v>2010</v>
       </c>
-      <c r="B6" s="23">
+      <c r="B6" s="16">
         <v>761621104.20000005</v>
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="22">
+      <c r="A7" s="15">
         <v>2011</v>
       </c>
-      <c r="B7" s="23">
+      <c r="B7" s="16">
         <v>622451671.72000003</v>
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="22">
+      <c r="A8" s="15">
         <v>2012</v>
       </c>
-      <c r="B8" s="23">
+      <c r="B8" s="16">
         <v>671275311.88999999</v>
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="22">
+      <c r="A9" s="15">
         <v>2013</v>
       </c>
-      <c r="B9" s="23">
+      <c r="B9" s="16">
         <v>606111615.41999996</v>
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="22">
+      <c r="A10" s="15">
         <v>2014</v>
       </c>
-      <c r="B10" s="23">
+      <c r="B10" s="16">
         <v>634367865.74000001</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="22">
+      <c r="A11" s="15">
         <v>2015</v>
       </c>
-      <c r="B11" s="23">
+      <c r="B11" s="16">
         <v>620295262</v>
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="22">
+      <c r="A12" s="15">
         <v>2011</v>
       </c>
-      <c r="B12" s="23">
+      <c r="B12" s="16">
         <v>159099238</v>
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="22">
+      <c r="A13" s="15">
         <v>2012</v>
       </c>
-      <c r="B13" s="24">
+      <c r="B13" s="17">
         <v>159099238</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="22">
+      <c r="A14" s="15">
         <v>2013</v>
       </c>
-      <c r="B14" s="24">
+      <c r="B14" s="17">
         <v>136203956</v>
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="22">
+      <c r="A15" s="15">
         <v>2014</v>
       </c>
-      <c r="B15" s="24">
+      <c r="B15" s="17">
         <v>170181166</v>
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="22">
+      <c r="A16" s="15">
         <v>2015</v>
       </c>
-      <c r="B16" s="24">
+      <c r="B16" s="17">
         <v>157885429</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="22">
+    <row r="17" spans="1:10">
+      <c r="A17" s="15">
         <v>2016</v>
       </c>
-      <c r="B17" s="24">
+      <c r="B17" s="17">
         <v>234428859</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="22">
+    <row r="18" spans="1:10">
+      <c r="A18" s="15">
         <v>2017</v>
       </c>
-      <c r="B18" s="24">
+      <c r="B18" s="17">
         <v>221098119</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="22">
+    <row r="19" spans="1:10">
+      <c r="A19" s="15">
         <v>2016</v>
       </c>
-      <c r="B19" s="23">
+      <c r="B19" s="16">
         <v>377344006.02999997</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="22">
+    <row r="20" spans="1:10">
+      <c r="A20" s="15">
         <v>2017</v>
       </c>
-      <c r="B20" s="24">
+      <c r="B20" s="17">
         <v>391656866.92000002</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="22">
+    <row r="21" spans="1:10">
+      <c r="A21" s="15">
         <v>2018</v>
       </c>
-      <c r="B21" s="23">
+      <c r="B21" s="16">
         <v>345428734.49000001</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="22">
+    <row r="22" spans="1:10">
+      <c r="A22" s="15">
         <v>2019</v>
       </c>
-      <c r="B22" s="24">
+      <c r="B22" s="17">
         <v>173538420.53999999</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="22">
+    <row r="23" spans="1:10">
+      <c r="A23" s="15">
         <v>2018</v>
       </c>
-      <c r="B23" s="23">
+      <c r="B23" s="16">
         <v>232957994</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="22">
+    <row r="24" spans="1:10">
+      <c r="A24" s="15">
         <v>2019</v>
       </c>
-      <c r="B24" s="24">
+      <c r="B24" s="17">
         <v>237138558</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="22">
+    <row r="25" spans="1:10">
+      <c r="A25" s="15">
         <v>2020</v>
       </c>
-      <c r="B25" s="24">
+      <c r="B25" s="17">
         <v>227389933</v>
       </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="25" t="s">
+      <c r="J25" s="10"/>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B26" s="26">
+      <c r="B26" s="19">
         <f>AVERAGE(B2:B25)</f>
         <v>389540604.13541669</v>
       </c>
       <c r="E26" s="10"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="E31" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5077,4 +5401,558 @@
   </mergeCells>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62090D6-4474-48C5-9F40-1D3B54A5A11B}">
+  <dimension ref="A1:L20"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.140625" customWidth="1"/>
+    <col min="8" max="8" width="21.28515625" customWidth="1"/>
+    <col min="9" max="9" width="23.7109375" customWidth="1"/>
+    <col min="10" max="10" width="23.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="33.75" customHeight="1">
+      <c r="A1" s="22" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>35</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="F1" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="G1" s="23" t="s">
+        <v>38</v>
+      </c>
+      <c r="H1" s="23" t="s">
+        <v>39</v>
+      </c>
+      <c r="I1" s="23" t="s">
+        <v>40</v>
+      </c>
+      <c r="J1" s="23" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B2" s="25">
+        <v>2022</v>
+      </c>
+      <c r="C2" s="26">
+        <v>505515269</v>
+      </c>
+      <c r="D2" s="26">
+        <v>669986245.77510929</v>
+      </c>
+      <c r="E2" s="26">
+        <f>D2+(D2*-0.0418627619890395)</f>
+        <v>641938771.03229582</v>
+      </c>
+      <c r="F2" s="26">
+        <v>56649599.733598158</v>
+      </c>
+      <c r="G2" s="26">
+        <f>E2+F2</f>
+        <v>698588370.76589394</v>
+      </c>
+      <c r="H2" s="27">
+        <f>G2*1.009</f>
+        <v>704875666.1027869</v>
+      </c>
+      <c r="I2" s="27">
+        <f>C2-H2</f>
+        <v>-199360397.1027869</v>
+      </c>
+      <c r="J2" s="32">
+        <f>((I2/C2)*100)*-1</f>
+        <v>39.437067350538705</v>
+      </c>
+      <c r="L2" s="10"/>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="25">
+        <v>2023</v>
+      </c>
+      <c r="C3" s="26">
+        <v>505515269</v>
+      </c>
+      <c r="D3" s="26">
+        <v>413560041.77863795</v>
+      </c>
+      <c r="E3" s="26">
+        <f>D3+(D3*-0.0418627619890395)</f>
+        <v>396247276.1814816</v>
+      </c>
+      <c r="F3" s="26">
+        <v>46754807.064309984</v>
+      </c>
+      <c r="G3" s="26">
+        <f>E3+F3</f>
+        <v>443002083.24579155</v>
+      </c>
+      <c r="H3" s="27">
+        <f>G3*1.009</f>
+        <v>446989101.99500364</v>
+      </c>
+      <c r="I3" s="27">
+        <f t="shared" ref="I3:I15" si="0">C3-H3</f>
+        <v>58526167.004996359</v>
+      </c>
+      <c r="J3" s="32">
+        <f t="shared" ref="J3:J15" si="1">((I3/C3)*100)*-1</f>
+        <v>-11.577527048939912</v>
+      </c>
+      <c r="L3" s="10"/>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4" s="28">
+        <v>2022</v>
+      </c>
+      <c r="C4" s="29">
+        <v>26242349</v>
+      </c>
+      <c r="D4" s="29">
+        <v>32838548.390269801</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H4" s="24">
+        <f>D4*1.01864506967843</f>
+        <v>33450825.413144875</v>
+      </c>
+      <c r="I4" s="27">
+        <f t="shared" si="0"/>
+        <v>-7208476.4131448753</v>
+      </c>
+      <c r="J4" s="32">
+        <f t="shared" si="1"/>
+        <v>27.468868785888318</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="28">
+        <v>2023</v>
+      </c>
+      <c r="C5" s="29">
+        <v>26242349</v>
+      </c>
+      <c r="D5" s="29">
+        <v>40240432.344496213</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G5" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H5" s="24">
+        <f>D5*1.01864506967843</f>
+        <v>40990718.009449489</v>
+      </c>
+      <c r="I5" s="27">
+        <f t="shared" si="0"/>
+        <v>-14748369.009449489</v>
+      </c>
+      <c r="J5" s="32">
+        <f t="shared" si="1"/>
+        <v>56.200643507368532</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B6" s="25">
+        <v>2022</v>
+      </c>
+      <c r="C6" s="26">
+        <v>97048732</v>
+      </c>
+      <c r="D6" s="26">
+        <v>147102865.80102536</v>
+      </c>
+      <c r="E6" s="26">
+        <f>D6+(D6*-0.0880887103579795)</f>
+        <v>134144764.06265011</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H6" s="27">
+        <f>E6*0.994609286576602</f>
+        <v>133421628.08233902</v>
+      </c>
+      <c r="I6" s="27">
+        <f t="shared" si="0"/>
+        <v>-36372896.082339019</v>
+      </c>
+      <c r="J6" s="32">
+        <f t="shared" si="1"/>
+        <v>37.479001871285675</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="B7" s="25">
+        <v>2023</v>
+      </c>
+      <c r="C7" s="26">
+        <v>97048732</v>
+      </c>
+      <c r="D7" s="26">
+        <v>148357550.29244328</v>
+      </c>
+      <c r="E7" s="26">
+        <f>D7+(D7*-0.0880887103579795)</f>
+        <v>135288925.01531285</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H7" s="27">
+        <f>E7*0.994609286576602</f>
+        <v>134559621.19119573</v>
+      </c>
+      <c r="I7" s="27">
+        <f t="shared" si="0"/>
+        <v>-37510889.191195726</v>
+      </c>
+      <c r="J7" s="32">
+        <f t="shared" si="1"/>
+        <v>38.651601538900813</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B8" s="28">
+        <v>2022</v>
+      </c>
+      <c r="C8" s="29">
+        <v>34660570</v>
+      </c>
+      <c r="D8" s="29">
+        <v>37566082.745758325</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F8" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G8" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24">
+        <f>D8*0.99952133701608</f>
+        <v>37548101.252497055</v>
+      </c>
+      <c r="I8" s="27">
+        <f t="shared" si="0"/>
+        <v>-2887531.2524970546</v>
+      </c>
+      <c r="J8" s="32">
+        <f t="shared" si="1"/>
+        <v>8.3308821883109676</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="28">
+        <v>2023</v>
+      </c>
+      <c r="C9" s="29">
+        <v>34660570</v>
+      </c>
+      <c r="D9" s="29">
+        <v>23869957.944272775</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F9" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G9" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H9" s="24">
+        <f>D9*0.99952133701608</f>
+        <v>23858532.278977126</v>
+      </c>
+      <c r="I9" s="27">
+        <f t="shared" si="0"/>
+        <v>10802037.721022874</v>
+      </c>
+      <c r="J9" s="32">
+        <f t="shared" si="1"/>
+        <v>-31.165205076035608</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="25">
+        <v>2022</v>
+      </c>
+      <c r="C10" s="26">
+        <v>4062706</v>
+      </c>
+      <c r="D10" s="26">
+        <v>4272152.1043191897</v>
+      </c>
+      <c r="E10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H10" s="27">
+        <f>D10*0.966126945902574</f>
+        <v>4127441.2649771534</v>
+      </c>
+      <c r="I10" s="27">
+        <f t="shared" si="0"/>
+        <v>-64735.264977153391</v>
+      </c>
+      <c r="J10" s="32">
+        <f t="shared" si="1"/>
+        <v>1.5934026478202801</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B11" s="25">
+        <v>2023</v>
+      </c>
+      <c r="C11" s="26">
+        <v>4062706</v>
+      </c>
+      <c r="D11" s="26">
+        <v>2436966.2195611498</v>
+      </c>
+      <c r="E11" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="F11" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="H11" s="27">
+        <f>D11*0.966126945902574</f>
+        <v>2354418.7309723552</v>
+      </c>
+      <c r="I11" s="27">
+        <f t="shared" si="0"/>
+        <v>1708287.2690276448</v>
+      </c>
+      <c r="J11" s="32">
+        <f t="shared" si="1"/>
+        <v>-42.04801600282287</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B12" s="28">
+        <v>2022</v>
+      </c>
+      <c r="C12" s="29">
+        <v>6036837</v>
+      </c>
+      <c r="D12" s="29">
+        <v>6565583.4685837105</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F12" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G12" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H12" s="24">
+        <f>D12*1.00176723976846</f>
+        <v>6577186.4287925353</v>
+      </c>
+      <c r="I12" s="27">
+        <f t="shared" si="0"/>
+        <v>-540349.42879253533</v>
+      </c>
+      <c r="J12" s="32">
+        <f t="shared" si="1"/>
+        <v>8.9508699471682824</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B13" s="28">
+        <v>2023</v>
+      </c>
+      <c r="C13" s="29">
+        <v>6036837</v>
+      </c>
+      <c r="D13" s="29">
+        <v>8167617.3688533697</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="F13" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G13" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="H13" s="24">
+        <f>D13*1.00176723976846</f>
+        <v>8182051.5070811724</v>
+      </c>
+      <c r="I13" s="27">
+        <f t="shared" si="0"/>
+        <v>-2145214.5070811724</v>
+      </c>
+      <c r="J13" s="32">
+        <f t="shared" si="1"/>
+        <v>35.535405495976988</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B14" s="25">
+        <v>2022</v>
+      </c>
+      <c r="C14" s="26">
+        <v>673566464</v>
+      </c>
+      <c r="D14" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F14" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="G14" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H14" s="30">
+        <f>H2+H6+H4+H8+H10+H12</f>
+        <v>920000848.54453743</v>
+      </c>
+      <c r="I14" s="27">
+        <f t="shared" si="0"/>
+        <v>-246434384.54453743</v>
+      </c>
+      <c r="J14" s="32">
+        <f t="shared" si="1"/>
+        <v>36.586498544045305</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="B15" s="25">
+        <v>2023</v>
+      </c>
+      <c r="C15" s="26">
+        <v>673566464</v>
+      </c>
+      <c r="D15" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="F15" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="G15" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="H15" s="30">
+        <f>H3+H7+H5+H9+H11+H13</f>
+        <v>656934443.71267962</v>
+      </c>
+      <c r="I15" s="27">
+        <f t="shared" si="0"/>
+        <v>16632020.287320375</v>
+      </c>
+      <c r="J15" s="32">
+        <f t="shared" si="1"/>
+        <v>-2.4692470864048803</v>
+      </c>
+    </row>
+    <row r="20" spans="10:10">
+      <c r="J20" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/results/results_vfinal.xlsx
+++ b/results/results_vfinal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Celso\Documents\GitHub\Brazil-National-FREL\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipamamazonia-my.sharepoint.com/personal/celso_junior_ipam_org_br/Documents/Documentos/GitHub/Brazil-National-FREL/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2C95EF-3402-44DC-AD55-6CFF0EAF20AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{BF2C95EF-3402-44DC-AD55-6CFF0EAF20AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{749A3931-4591-4CA2-A0D8-5F37CED72160}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="29775" windowHeight="15585" tabRatio="761" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38520" yWindow="-105" windowWidth="38640" windowHeight="15720" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 1" sheetId="11" r:id="rId1"/>
@@ -21,7 +21,6 @@
     <sheet name="2022 and 2023 Emissions" sheetId="19" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1533,6 +1532,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1540,7 +1540,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -2699,6 +2698,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -2706,7 +2706,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4196,18 +4195,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{746E9525-7C4D-42FA-A23D-D0CEA7AFCD11}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.140625" customWidth="1"/>
-    <col min="2" max="2" width="4.140625" customWidth="1"/>
-    <col min="3" max="3" width="23.28515625" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" customWidth="1"/>
-    <col min="5" max="5" width="4.7109375" customWidth="1"/>
-    <col min="6" max="6" width="32.140625" customWidth="1"/>
-    <col min="7" max="7" width="31.28515625" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="1" max="1" width="10.109375" customWidth="1"/>
+    <col min="2" max="2" width="4.109375" customWidth="1"/>
+    <col min="3" max="3" width="23.33203125" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" customWidth="1"/>
+    <col min="5" max="5" width="4.6640625" customWidth="1"/>
+    <col min="6" max="6" width="32.109375" customWidth="1"/>
+    <col min="7" max="7" width="31.33203125" customWidth="1"/>
+    <col min="8" max="8" width="29.44140625" customWidth="1"/>
     <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.140625" customWidth="1"/>
+    <col min="11" max="11" width="19.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="48.75" customHeight="1">
@@ -4344,10 +4343,7 @@
         <v>673566464</v>
       </c>
       <c r="J7" s="1"/>
-      <c r="K7" s="1">
-        <f>H7-G7</f>
-        <v>-246434384.54453743</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="10"/>
     </row>
     <row r="8" spans="1:12">
@@ -4369,10 +4365,7 @@
         <v>673566464</v>
       </c>
       <c r="J8" s="1"/>
-      <c r="K8" s="1">
-        <f>H8-G8</f>
-        <v>16632020.287320375</v>
-      </c>
+      <c r="K8" s="1"/>
       <c r="L8" s="10"/>
     </row>
     <row r="11" spans="1:12">
@@ -4450,18 +4443,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A3ACF42-74B5-4EF7-B6B3-6008AC5E4E20}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="36.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.42578125" customWidth="1"/>
-    <col min="4" max="4" width="28.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" customWidth="1"/>
-    <col min="6" max="6" width="32.28515625" customWidth="1"/>
-    <col min="7" max="7" width="30.42578125" customWidth="1"/>
-    <col min="8" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5703125" customWidth="1"/>
-    <col min="13" max="13" width="13.140625" customWidth="1"/>
+    <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="39.44140625" customWidth="1"/>
+    <col min="4" max="4" width="28.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" customWidth="1"/>
+    <col min="6" max="6" width="32.33203125" customWidth="1"/>
+    <col min="7" max="7" width="30.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.6640625" customWidth="1"/>
+    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5546875" customWidth="1"/>
+    <col min="13" max="13" width="13.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -4646,22 +4639,10 @@
         <f>B7+C7</f>
         <v>983210182.69670343</v>
       </c>
-      <c r="I7" s="1">
-        <f>D7-H7</f>
-        <v>-253756227.12114453</v>
-      </c>
-      <c r="K7" s="1">
-        <f>'Figure 1'!K7</f>
-        <v>-246434384.54453743</v>
-      </c>
-      <c r="M7" s="1">
-        <f>(I7*-1)-(K7*-1)</f>
-        <v>7321842.5766071081</v>
-      </c>
-      <c r="O7" s="2">
-        <f>M7/(K7*-1)*100</f>
-        <v>2.9711124079293616</v>
-      </c>
+      <c r="I7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="M7" s="1"/>
+      <c r="O7" s="2"/>
     </row>
     <row r="8" spans="1:15">
       <c r="A8" s="7">
@@ -4689,22 +4670,10 @@
         <f t="shared" si="0"/>
         <v>726126998.48932421</v>
       </c>
-      <c r="I8" s="1">
-        <f>D8-H8</f>
-        <v>3326957.0862346888</v>
-      </c>
-      <c r="K8" s="1">
-        <f>'Figure 1'!K8</f>
-        <v>16632020.287320375</v>
-      </c>
-      <c r="M8" s="1">
-        <f>(K8)-(I8)</f>
-        <v>13305063.201085687</v>
-      </c>
-      <c r="O8" s="2">
-        <f>M8/(K8)*100</f>
-        <v>79.996674915247453</v>
-      </c>
+      <c r="I8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="M8" s="1"/>
+      <c r="O8" s="2"/>
     </row>
     <row r="11" spans="1:15">
       <c r="A11" s="3"/>
@@ -4725,110 +4694,63 @@
       <c r="B14" s="4"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
-      <c r="L14" s="2">
-        <f>'Figure 1'!D2/'Figure 4'!C2*100</f>
-        <v>35.654804825495098</v>
-      </c>
+      <c r="L14" s="2"/>
     </row>
     <row r="15" spans="1:15">
       <c r="A15" s="3"/>
       <c r="B15" s="4"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
-      <c r="L15" s="2">
-        <f>'Figure 1'!D3/'Figure 4'!C3*100</f>
-        <v>27.023722056340905</v>
-      </c>
+      <c r="L15" s="2"/>
     </row>
     <row r="16" spans="1:15">
       <c r="A16" s="3"/>
       <c r="B16" s="4"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
-      <c r="L16" s="2">
-        <f>'Figure 1'!D4/'Figure 4'!C4*100</f>
-        <v>33.463662956250403</v>
-      </c>
+      <c r="L16" s="2"/>
     </row>
     <row r="17" spans="1:12">
       <c r="A17" s="3"/>
       <c r="B17" s="4"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
-      <c r="L17" s="2">
-        <f>'Figure 1'!D5/'Figure 4'!C5*100</f>
-        <v>41.23688655835786</v>
-      </c>
+      <c r="L17" s="2"/>
     </row>
     <row r="18" spans="1:12">
       <c r="A18" s="3"/>
       <c r="B18" s="4"/>
-      <c r="L18" s="2">
-        <f>'Figure 1'!D6/'Figure 4'!C6*100</f>
-        <v>55.930257812717443</v>
-      </c>
+      <c r="L18" s="2"/>
     </row>
     <row r="20" spans="1:12">
-      <c r="L20" s="2">
-        <f>AVERAGE(L14:L18)</f>
-        <v>38.661866841832342</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12">
-      <c r="G22">
-        <v>673566464</v>
-      </c>
+      <c r="L20" s="2"/>
     </row>
     <row r="24" spans="1:12">
-      <c r="G24" s="1">
-        <f>D8-G22</f>
-        <v>55887491.575558901</v>
-      </c>
+      <c r="G24" s="1"/>
     </row>
     <row r="25" spans="1:12">
-      <c r="G25" s="33">
-        <f>G24/G22*100</f>
-        <v>8.2972497240537937</v>
-      </c>
+      <c r="G25" s="33"/>
     </row>
     <row r="29" spans="1:12">
-      <c r="G29" s="2">
-        <f>C2/'Figure 1'!D2</f>
-        <v>2.8046710812029083</v>
-      </c>
+      <c r="G29" s="2"/>
     </row>
     <row r="30" spans="1:12">
-      <c r="G30" s="2">
-        <f>C3/'Figure 1'!D3</f>
-        <v>3.7004525058211137</v>
-      </c>
+      <c r="G30" s="2"/>
     </row>
     <row r="31" spans="1:12">
       <c r="D31" s="1"/>
-      <c r="G31" s="2">
-        <f>C4/'Figure 1'!D4</f>
-        <v>2.98831601701038</v>
-      </c>
+      <c r="G31" s="2"/>
     </row>
     <row r="32" spans="1:12">
-      <c r="G32" s="2">
-        <f>C5/'Figure 1'!D5</f>
-        <v>2.4250133399009504</v>
-      </c>
+      <c r="G32" s="2"/>
     </row>
     <row r="33" spans="4:7">
       <c r="D33" s="1"/>
-      <c r="G33" s="2">
-        <f>C6/'Figure 1'!D6</f>
-        <v>1.7879409806200099</v>
-      </c>
+      <c r="G33" s="2"/>
     </row>
     <row r="34" spans="4:7">
       <c r="D34" s="2"/>
-      <c r="G34" s="2">
-        <f>AVERAGE(G29:G33)</f>
-        <v>2.741278784911072</v>
-      </c>
+      <c r="G34" s="2"/>
     </row>
     <row r="35" spans="4:7">
       <c r="G35" s="2"/>
@@ -4851,12 +4773,12 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DDE237F-5805-4F40-85AC-796F9BE5D6ED}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.140625" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+    <col min="1" max="1" width="8.109375" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="49.5" customHeight="1">
@@ -4865,7 +4787,7 @@
       </c>
       <c r="B1" s="35"/>
     </row>
-    <row r="2" spans="1:9" ht="17.25">
+    <row r="2" spans="1:9" ht="16.2">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -4973,13 +4895,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF00FE4-336D-4E92-B05B-E6E1C4CE89EE}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="8.140625" customWidth="1"/>
-    <col min="2" max="2" width="21.42578125" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5703125" customWidth="1"/>
-    <col min="10" max="10" width="8.28515625" customWidth="1"/>
+    <col min="1" max="1" width="8.109375" customWidth="1"/>
+    <col min="2" max="2" width="21.44140625" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" customWidth="1"/>
+    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="10" max="10" width="8.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
@@ -4989,7 +4911,7 @@
       </c>
       <c r="C1" s="38"/>
     </row>
-    <row r="2" spans="1:13" ht="17.25">
+    <row r="2" spans="1:13" ht="16.2">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -5165,14 +5087,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8347AE-1F9E-406B-BBBE-0167BC334EA0}">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="24.28515625" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.33203125" customWidth="1"/>
+    <col min="2" max="2" width="18.88671875" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.5">
+    <row r="1" spans="1:10" ht="16.2">
       <c r="A1" s="14" t="s">
         <v>20</v>
       </c>
@@ -5406,17 +5328,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62090D6-4474-48C5-9F40-1D3B54A5A11B}">
   <dimension ref="A1:L20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="28.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.140625" customWidth="1"/>
-    <col min="8" max="8" width="21.28515625" customWidth="1"/>
-    <col min="9" max="9" width="23.7109375" customWidth="1"/>
-    <col min="10" max="10" width="23.85546875" customWidth="1"/>
+    <col min="3" max="3" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.109375" customWidth="1"/>
+    <col min="8" max="8" width="21.33203125" customWidth="1"/>
+    <col min="9" max="9" width="23.6640625" customWidth="1"/>
+    <col min="10" max="10" width="23.88671875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33.75" customHeight="1">

--- a/results/results_vfinal.xlsx
+++ b/results/results_vfinal.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipamamazonia-my.sharepoint.com/personal/celso_junior_ipam_org_br/Documents/Documentos/GitHub/Brazil-National-FREL/results/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/celsojunior/Documents/GitHub/Brazil-National-FREL/results/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{BF2C95EF-3402-44DC-AD55-6CFF0EAF20AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{749A3931-4591-4CA2-A0D8-5F37CED72160}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B36B80CB-3CD0-5149-9BDE-6A955437DA49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-105" windowWidth="38640" windowHeight="15720" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="200" yWindow="680" windowWidth="18500" windowHeight="17820" tabRatio="761" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Figure 1" sheetId="11" r:id="rId1"/>
@@ -665,6 +665,12 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFD55E00"/>
+      <color rgb="FF56B4E9"/>
+      <color rgb="FF0072B2"/>
+      <color rgb="FF1A1A1A"/>
+      <color rgb="FF333333"/>
+      <color rgb="FFE69F00"/>
       <color rgb="FFDE6C6A"/>
       <color rgb="FFE8C75A"/>
       <color rgb="FFF5F4EB"/>
@@ -718,9 +724,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="DE6C6A">
-                <a:alpha val="50196"/>
-              </a:srgbClr>
+              <a:srgbClr val="E69F00"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -738,18 +742,13 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="1A1A1A"/>
                     </a:solidFill>
                     <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -853,7 +852,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="DE6C6A"/>
+              <a:srgbClr val="0072B2"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -871,18 +870,13 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                      </a:schemeClr>
+                      <a:schemeClr val="bg1"/>
                     </a:solidFill>
                     <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1136,18 +1130,13 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
                   <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="333333"/>
                     </a:solidFill>
                     <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1295,10 +1284,7 @@
             <a:pPr>
               <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="85000"/>
-                    <a:lumOff val="15000"/>
-                  </a:schemeClr>
+                  <a:srgbClr val="333333"/>
                 </a:solidFill>
                 <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1333,10 +1319,7 @@
                 <a:pPr>
                   <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="333333"/>
                     </a:solidFill>
                     <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1344,22 +1327,9 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR" sz="1200" b="0" i="0" u="none" strike="noStrike" baseline="0"/>
-                  <a:t>tons</a:t>
+                  <a:rPr lang="pt-BR"/>
+                  <a:t>tons CO2 eq</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="pt-BR" baseline="0"/>
-                  <a:t> CO</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="pt-BR" baseline="-25000"/>
-                  <a:t>2</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="pt-BR" baseline="0"/>
-                  <a:t> eq</a:t>
-                </a:r>
-                <a:endParaRPr lang="pt-BR"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1378,10 +1348,7 @@
               <a:pPr>
                 <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="85000"/>
-                      <a:lumOff val="15000"/>
-                    </a:schemeClr>
+                    <a:srgbClr val="333333"/>
                   </a:solidFill>
                   <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
@@ -1415,10 +1382,7 @@
             <a:pPr>
               <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="85000"/>
-                    <a:lumOff val="15000"/>
-                  </a:schemeClr>
+                  <a:srgbClr val="333333"/>
                 </a:solidFill>
                 <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
@@ -1442,10 +1406,7 @@
                   <a:pPr>
                     <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                       <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="85000"/>
-                          <a:lumOff val="15000"/>
-                        </a:schemeClr>
+                        <a:srgbClr val="333333"/>
                       </a:solidFill>
                       <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
                       <a:ea typeface="+mn-ea"/>
@@ -1453,9 +1414,7 @@
                     </a:defRPr>
                   </a:pPr>
                   <a:r>
-                    <a:rPr lang="pt-BR" b="0" i="0">
-                      <a:effectLst/>
-                    </a:rPr>
+                    <a:rPr lang="pt-BR"/>
                     <a:t>Millions</a:t>
                   </a:r>
                 </a:p>
@@ -1475,10 +1434,7 @@
                 <a:pPr>
                   <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                      </a:schemeClr>
+                      <a:srgbClr val="333333"/>
                     </a:solidFill>
                     <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1516,10 +1472,7 @@
           <a:pPr>
             <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="85000"/>
-                  <a:lumOff val="15000"/>
-                </a:schemeClr>
+                <a:srgbClr val="333333"/>
               </a:solidFill>
               <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
               <a:ea typeface="+mn-ea"/>
@@ -1558,10 +1511,7 @@
       <a:pPr>
         <a:defRPr sz="1200">
           <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
+            <a:srgbClr val="333333"/>
           </a:solidFill>
           <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
         </a:defRPr>
@@ -1614,7 +1564,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="E8C75A"/>
+              <a:srgbClr val="0072B2"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1639,10 +1589,7 @@
                 <a:pPr>
                   <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="85000"/>
-                        <a:lumOff val="15000"/>
-                      </a:schemeClr>
+                      <a:schemeClr val="bg1"/>
                     </a:solidFill>
                     <a:latin typeface="Montserrat" pitchFamily="2" charset="0"/>
                     <a:ea typeface="+mn-ea"/>
@@ -1761,9 +1708,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="E8C75A">
-                <a:alpha val="50196"/>
-              </a:srgbClr>
+              <a:srgbClr val="56B4E9"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -2351,7 +2296,7 @@
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
-                <a:srgbClr val="DE6C6A"/>
+                <a:srgbClr val="D55E00"/>
               </a:solidFill>
               <a:prstDash val="solid"/>
               <a:round/>
@@ -2363,11 +2308,11 @@
             <c:size val="5"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="DE6C6A"/>
+                <a:srgbClr val="D55E00"/>
               </a:solidFill>
               <a:ln w="28575">
                 <a:solidFill>
-                  <a:srgbClr val="DE6C6A"/>
+                  <a:srgbClr val="D55E00"/>
                 </a:solidFill>
                 <a:prstDash val="solid"/>
               </a:ln>
@@ -4195,18 +4140,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{746E9525-7C4D-42FA-A23D-D0CEA7AFCD11}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.109375" customWidth="1"/>
-    <col min="2" max="2" width="4.109375" customWidth="1"/>
+    <col min="1" max="1" width="10.1640625" customWidth="1"/>
+    <col min="2" max="2" width="4.1640625" customWidth="1"/>
     <col min="3" max="3" width="23.33203125" customWidth="1"/>
-    <col min="4" max="4" width="24.44140625" customWidth="1"/>
+    <col min="4" max="4" width="24.5" customWidth="1"/>
     <col min="5" max="5" width="4.6640625" customWidth="1"/>
-    <col min="6" max="6" width="32.109375" customWidth="1"/>
+    <col min="6" max="6" width="32.1640625" customWidth="1"/>
     <col min="7" max="7" width="31.33203125" customWidth="1"/>
-    <col min="8" max="8" width="29.44140625" customWidth="1"/>
+    <col min="8" max="8" width="29.5" customWidth="1"/>
     <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="19.109375" customWidth="1"/>
+    <col min="11" max="11" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="48.75" customHeight="1">
@@ -4443,18 +4388,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A3ACF42-74B5-4EF7-B6B3-6008AC5E4E20}">
   <dimension ref="A1:O41"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="39.44140625" customWidth="1"/>
-    <col min="4" max="4" width="28.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" customWidth="1"/>
+    <col min="3" max="3" width="39.5" customWidth="1"/>
+    <col min="4" max="4" width="28.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.5" customWidth="1"/>
     <col min="6" max="6" width="32.33203125" customWidth="1"/>
-    <col min="7" max="7" width="30.44140625" customWidth="1"/>
+    <col min="7" max="7" width="30.5" customWidth="1"/>
     <col min="8" max="8" width="10.6640625" customWidth="1"/>
-    <col min="9" max="9" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.5546875" customWidth="1"/>
-    <col min="13" max="13" width="13.109375" customWidth="1"/>
+    <col min="9" max="9" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15">
@@ -4773,21 +4718,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5DDE237F-5805-4F40-85AC-796F9BE5D6ED}">
   <dimension ref="A1:I13"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.109375" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="1" max="1" width="8.1640625" customWidth="1"/>
+    <col min="2" max="2" width="73" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
     <col min="10" max="10" width="8.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="49.5" customHeight="1">
+    <row r="1" spans="1:9" ht="27" customHeight="1">
       <c r="A1" s="34" t="s">
         <v>14</v>
       </c>
       <c r="B1" s="35"/>
     </row>
-    <row r="2" spans="1:9" ht="16.2">
+    <row r="2" spans="1:9" ht="17">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -4895,12 +4840,12 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF00FE4-336D-4E92-B05B-E6E1C4CE89EE}">
   <dimension ref="A1:M19"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8.109375" customWidth="1"/>
-    <col min="2" max="2" width="21.44140625" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" customWidth="1"/>
-    <col min="8" max="8" width="10.5546875" customWidth="1"/>
+    <col min="1" max="1" width="8.1640625" customWidth="1"/>
+    <col min="2" max="2" width="21.5" customWidth="1"/>
+    <col min="3" max="3" width="21.1640625" customWidth="1"/>
+    <col min="8" max="8" width="10.5" customWidth="1"/>
     <col min="10" max="10" width="8.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4911,7 +4856,7 @@
       </c>
       <c r="C1" s="38"/>
     </row>
-    <row r="2" spans="1:13" ht="16.2">
+    <row r="2" spans="1:13" ht="17">
       <c r="A2" s="9" t="s">
         <v>0</v>
       </c>
@@ -5087,14 +5032,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B8347AE-1F9E-406B-BBBE-0167BC334EA0}">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24.33203125" customWidth="1"/>
-    <col min="2" max="2" width="18.88671875" customWidth="1"/>
-    <col min="5" max="5" width="10.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="16.2">
+    <row r="1" spans="1:10" ht="18">
       <c r="A1" s="14" t="s">
         <v>20</v>
       </c>
@@ -5328,17 +5273,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C62090D6-4474-48C5-9F40-1D3B54A5A11B}">
   <dimension ref="A1:L20"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.1640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="26.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="28.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.109375" customWidth="1"/>
+    <col min="7" max="7" width="21.1640625" customWidth="1"/>
     <col min="8" max="8" width="21.33203125" customWidth="1"/>
     <col min="9" max="9" width="23.6640625" customWidth="1"/>
-    <col min="10" max="10" width="23.88671875" customWidth="1"/>
+    <col min="10" max="10" width="23.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="33.75" customHeight="1">
